--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/PENNSYLVANIA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/PENNSYLVANIA_2014.xlsx
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C175">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C494">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C511">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C845">
